--- a/data/nzd0478/nzd0478.xlsx
+++ b/data/nzd0478/nzd0478.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J638"/>
+  <dimension ref="A1:J640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23412,6 +23412,78 @@
       <c r="J638" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>337.68</v>
+      </c>
+      <c r="C639" t="n">
+        <v>333.11</v>
+      </c>
+      <c r="D639" t="n">
+        <v>326.75</v>
+      </c>
+      <c r="E639" t="n">
+        <v>328.55</v>
+      </c>
+      <c r="F639" t="n">
+        <v>331.52</v>
+      </c>
+      <c r="G639" t="n">
+        <v>330.05</v>
+      </c>
+      <c r="H639" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="I639" t="n">
+        <v>336.22</v>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>338.15</v>
+      </c>
+      <c r="C640" t="n">
+        <v>331.69</v>
+      </c>
+      <c r="D640" t="n">
+        <v>327.48</v>
+      </c>
+      <c r="E640" t="n">
+        <v>328.56</v>
+      </c>
+      <c r="F640" t="n">
+        <v>331.16</v>
+      </c>
+      <c r="G640" t="n">
+        <v>329.82</v>
+      </c>
+      <c r="H640" t="n">
+        <v>332.36</v>
+      </c>
+      <c r="I640" t="n">
+        <v>337.49</v>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23426,7 +23498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B722"/>
+  <dimension ref="A1:B725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30649,6 +30721,36 @@
       </c>
       <c r="B722" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -30817,28 +30919,28 @@
         <v>0.0471</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3830780961838511</v>
+        <v>-0.3833473921079347</v>
       </c>
       <c r="J2" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K2" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3739570589178763</v>
+        <v>0.3757941470180681</v>
       </c>
       <c r="M2" t="n">
-        <v>2.623636803472492</v>
+        <v>2.616679070952185</v>
       </c>
       <c r="N2" t="n">
-        <v>10.64522844862552</v>
+        <v>10.61257453320954</v>
       </c>
       <c r="O2" t="n">
-        <v>3.262702629512154</v>
+        <v>3.257694665435902</v>
       </c>
       <c r="P2" t="n">
-        <v>348.3844532143094</v>
+        <v>348.3877468290988</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30899,28 +31001,28 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3900553285871657</v>
+        <v>-0.3913305766169606</v>
       </c>
       <c r="J3" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K3" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3960361246771988</v>
+        <v>0.3988589268016761</v>
       </c>
       <c r="M3" t="n">
-        <v>2.469826636355893</v>
+        <v>2.468344868900582</v>
       </c>
       <c r="N3" t="n">
-        <v>10.05371451694809</v>
+        <v>10.03465749909565</v>
       </c>
       <c r="O3" t="n">
-        <v>3.170759296595704</v>
+        <v>3.167752752203941</v>
       </c>
       <c r="P3" t="n">
-        <v>344.5276950189713</v>
+        <v>344.5432985732688</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30981,28 +31083,28 @@
         <v>0.1531</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2662868919553295</v>
+        <v>-0.2693484474179753</v>
       </c>
       <c r="J4" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K4" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1100743693568019</v>
+        <v>0.112729224985306</v>
       </c>
       <c r="M4" t="n">
-        <v>3.992872389810548</v>
+        <v>3.994745640197275</v>
       </c>
       <c r="N4" t="n">
-        <v>24.84076944526437</v>
+        <v>24.82598627574419</v>
       </c>
       <c r="O4" t="n">
-        <v>4.984051509090207</v>
+        <v>4.982568240952069</v>
       </c>
       <c r="P4" t="n">
-        <v>338.6098317005054</v>
+        <v>338.6472844827701</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31063,28 +31165,28 @@
         <v>0.1453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4665101136170548</v>
+        <v>-0.4692994511677351</v>
       </c>
       <c r="J5" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K5" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5045031995030627</v>
+        <v>0.5077060835533302</v>
       </c>
       <c r="M5" t="n">
-        <v>2.352141682747221</v>
+        <v>2.3578171511873</v>
       </c>
       <c r="N5" t="n">
-        <v>9.261834451634556</v>
+        <v>9.28474747785342</v>
       </c>
       <c r="O5" t="n">
-        <v>3.04332621511966</v>
+        <v>3.047088360690156</v>
       </c>
       <c r="P5" t="n">
-        <v>344.9162049453523</v>
+        <v>344.9503287928316</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31141,28 +31243,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.421835147182871</v>
+        <v>-0.4228124071492854</v>
       </c>
       <c r="J6" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K6" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4638800052806639</v>
+        <v>0.4664666402133747</v>
       </c>
       <c r="M6" t="n">
-        <v>2.375074808946299</v>
+        <v>2.371782000002844</v>
       </c>
       <c r="N6" t="n">
-        <v>8.911274734723371</v>
+        <v>8.88984803636618</v>
       </c>
       <c r="O6" t="n">
-        <v>2.98517582978346</v>
+        <v>2.98158481958273</v>
       </c>
       <c r="P6" t="n">
-        <v>343.8674699796803</v>
+        <v>343.8794261083419</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31219,28 +31321,28 @@
         <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5481367120123328</v>
+        <v>-0.5502937901106931</v>
       </c>
       <c r="J7" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K7" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6607136654711201</v>
+        <v>0.6628847205830926</v>
       </c>
       <c r="M7" t="n">
-        <v>2.062697611377778</v>
+        <v>2.066357732561187</v>
       </c>
       <c r="N7" t="n">
-        <v>6.685421855484713</v>
+        <v>6.695569993563265</v>
       </c>
       <c r="O7" t="n">
-        <v>2.585618273350634</v>
+        <v>2.587579949211863</v>
       </c>
       <c r="P7" t="n">
-        <v>347.5135319034375</v>
+        <v>347.5399213203348</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31301,28 +31403,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5348547423067366</v>
+        <v>-0.5354837444612649</v>
       </c>
       <c r="J8" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K8" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5241609225470124</v>
+        <v>0.5262950727973791</v>
       </c>
       <c r="M8" t="n">
-        <v>2.662100629188803</v>
+        <v>2.656081303377947</v>
       </c>
       <c r="N8" t="n">
-        <v>11.25291721736027</v>
+        <v>11.22093594805938</v>
       </c>
       <c r="O8" t="n">
-        <v>3.354536811149979</v>
+        <v>3.349766551277772</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9200901992045</v>
+        <v>346.9277836358977</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -31383,28 +31485,28 @@
         <v>0.0601</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4044948515415852</v>
+        <v>-0.4049856821542421</v>
       </c>
       <c r="J9" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K9" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3636658112401209</v>
+        <v>0.3656787621583059</v>
       </c>
       <c r="M9" t="n">
-        <v>2.761814597647649</v>
+        <v>2.755248119780465</v>
       </c>
       <c r="N9" t="n">
-        <v>12.40528474244584</v>
+        <v>12.36934649469845</v>
       </c>
       <c r="O9" t="n">
-        <v>3.522113675400872</v>
+        <v>3.517008173817407</v>
       </c>
       <c r="P9" t="n">
-        <v>348.2119691461004</v>
+        <v>348.217971502304</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -31446,7 +31548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J638"/>
+  <dimension ref="A1:J640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64625,6 +64727,110 @@
         </is>
       </c>
     </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-45.216427386534264,170.8880365377723</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-45.21676228060126,170.88728346102383</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-45.2169857878851,170.88645610326085</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-45.21726435851798,170.8856463348317</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-45.21778102211066,170.88506750159618</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>-45.218328552260516,170.88458536489188</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>-45.218920588535404,170.88424255940387</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>-45.21951903232911,170.88394119787648</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-45.21643084987575,170.88803997221686</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-45.21675123329728,170.88727437584149</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-45.21699177482979,170.88645992794733</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-45.21726443126298,170.88564640977367</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-45.217779093532535,170.8850638188736</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>-45.218327580538514,170.88458277935277</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>-45.218923779919905,170.8842525346219</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>-45.21952374521326,170.8839559288581</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0478/nzd0478.xlsx
+++ b/data/nzd0478/nzd0478.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J640"/>
+  <dimension ref="A1:J641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23482,6 +23482,42 @@
         <v>337.49</v>
       </c>
       <c r="J640" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>338.07</v>
+      </c>
+      <c r="C641" t="n">
+        <v>331.57</v>
+      </c>
+      <c r="D641" t="n">
+        <v>327.61</v>
+      </c>
+      <c r="E641" t="n">
+        <v>327.74</v>
+      </c>
+      <c r="F641" t="n">
+        <v>330.62</v>
+      </c>
+      <c r="G641" t="n">
+        <v>329.27</v>
+      </c>
+      <c r="H641" t="n">
+        <v>332.25</v>
+      </c>
+      <c r="I641" t="n">
+        <v>337.33</v>
+      </c>
+      <c r="J641" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23498,7 +23534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B725"/>
+  <dimension ref="A1:B727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30751,6 +30787,26 @@
       </c>
       <c r="B725" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -30919,28 +30975,28 @@
         <v>0.0471</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3833473921079347</v>
+        <v>-0.3834259035940215</v>
       </c>
       <c r="J2" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K2" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3757941470180681</v>
+        <v>0.3766482727621386</v>
       </c>
       <c r="M2" t="n">
-        <v>2.616679070952185</v>
+        <v>2.612954140711783</v>
       </c>
       <c r="N2" t="n">
-        <v>10.61257453320954</v>
+        <v>10.59607516036365</v>
       </c>
       <c r="O2" t="n">
-        <v>3.257694665435902</v>
+        <v>3.255161310958898</v>
       </c>
       <c r="P2" t="n">
-        <v>348.3877468290988</v>
+        <v>348.3887084571402</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31001,28 +31057,28 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3913305766169606</v>
+        <v>-0.3922403487676768</v>
       </c>
       <c r="J3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3988589268016761</v>
+        <v>0.4004840681244188</v>
       </c>
       <c r="M3" t="n">
-        <v>2.468344868900582</v>
+        <v>2.468927445414539</v>
       </c>
       <c r="N3" t="n">
-        <v>10.03465749909565</v>
+        <v>10.03009303658518</v>
       </c>
       <c r="O3" t="n">
-        <v>3.167752752203941</v>
+        <v>3.167032212748266</v>
       </c>
       <c r="P3" t="n">
-        <v>344.5432985732688</v>
+        <v>344.5544416869072</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31083,28 +31139,28 @@
         <v>0.1531</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2693484474179753</v>
+        <v>-0.270691523821235</v>
       </c>
       <c r="J4" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K4" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112729224985306</v>
+        <v>0.113956173762371</v>
       </c>
       <c r="M4" t="n">
-        <v>3.994745640197275</v>
+        <v>3.994778196601261</v>
       </c>
       <c r="N4" t="n">
-        <v>24.82598627574419</v>
+        <v>24.81141898340174</v>
       </c>
       <c r="O4" t="n">
-        <v>4.982568240952069</v>
+        <v>4.981106200775259</v>
       </c>
       <c r="P4" t="n">
-        <v>338.6472844827701</v>
+        <v>338.6637348137401</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31165,28 +31221,28 @@
         <v>0.1453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4692994511677351</v>
+        <v>-0.4709518046694099</v>
       </c>
       <c r="J5" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K5" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5077060835533302</v>
+        <v>0.5092856291489938</v>
       </c>
       <c r="M5" t="n">
-        <v>2.3578171511873</v>
+        <v>2.361832623630658</v>
       </c>
       <c r="N5" t="n">
-        <v>9.28474747785342</v>
+        <v>9.306903904328621</v>
       </c>
       <c r="O5" t="n">
-        <v>3.047088360690156</v>
+        <v>3.050721866104582</v>
       </c>
       <c r="P5" t="n">
-        <v>344.9503287928316</v>
+        <v>344.9705672259662</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31243,28 +31299,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4228124071492854</v>
+        <v>-0.4235367526924727</v>
       </c>
       <c r="J6" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K6" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4664666402133747</v>
+        <v>0.4679272518197996</v>
       </c>
       <c r="M6" t="n">
-        <v>2.371782000002844</v>
+        <v>2.37117725489131</v>
       </c>
       <c r="N6" t="n">
-        <v>8.88984803636618</v>
+        <v>8.883003340830712</v>
       </c>
       <c r="O6" t="n">
-        <v>2.98158481958273</v>
+        <v>2.980436770144724</v>
       </c>
       <c r="P6" t="n">
-        <v>343.8794261083419</v>
+        <v>343.8882980711678</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31321,28 +31377,28 @@
         <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5502937901106931</v>
+        <v>-0.5515825024222067</v>
       </c>
       <c r="J7" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K7" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6628847205830926</v>
+        <v>0.6639086746616307</v>
       </c>
       <c r="M7" t="n">
-        <v>2.066357732561187</v>
+        <v>2.069212301421038</v>
       </c>
       <c r="N7" t="n">
-        <v>6.695569993563265</v>
+        <v>6.707410176461647</v>
       </c>
       <c r="O7" t="n">
-        <v>2.587579949211863</v>
+        <v>2.589866826008945</v>
       </c>
       <c r="P7" t="n">
-        <v>347.5399213203348</v>
+        <v>347.5557057865037</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31403,28 +31459,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5354837444612649</v>
+        <v>-0.5356823722645356</v>
       </c>
       <c r="J8" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K8" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5262950727973791</v>
+        <v>0.5272753098874021</v>
       </c>
       <c r="M8" t="n">
-        <v>2.656081303377947</v>
+        <v>2.65265735424289</v>
       </c>
       <c r="N8" t="n">
-        <v>11.22093594805938</v>
+        <v>11.20393303587971</v>
       </c>
       <c r="O8" t="n">
-        <v>3.349766551277772</v>
+        <v>3.347227664184154</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9277836358977</v>
+        <v>346.9302164782109</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -31485,28 +31541,28 @@
         <v>0.0601</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4049856821542421</v>
+        <v>-0.4050634792228224</v>
       </c>
       <c r="J9" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K9" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3656787621583059</v>
+        <v>0.3665177833003808</v>
       </c>
       <c r="M9" t="n">
-        <v>2.755248119780465</v>
+        <v>2.751270585707663</v>
       </c>
       <c r="N9" t="n">
-        <v>12.36934649469845</v>
+        <v>12.35010066609217</v>
       </c>
       <c r="O9" t="n">
-        <v>3.517008173817407</v>
+        <v>3.514271000661755</v>
       </c>
       <c r="P9" t="n">
-        <v>348.217971502304</v>
+        <v>348.2189243799835</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -31548,7 +31604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J640"/>
+  <dimension ref="A1:J641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64831,6 +64887,58 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-45.21643026037081,170.88803938763053</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-45.216750299722264,170.88727360807977</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-45.21699284099801,170.88646060905597</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-45.217258466172375,170.88564026453324</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-45.21777620066515,170.88505829479018</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>-45.218325256855245,170.88457659654225</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>-45.2189233717196,170.88425125872186</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>-45.21952315146418,170.88395407298626</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0478/nzd0478.xlsx
+++ b/data/nzd0478/nzd0478.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J641"/>
+  <dimension ref="A1:J642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23520,6 +23520,42 @@
       <c r="J641" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>340.57</v>
+      </c>
+      <c r="C642" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="D642" t="n">
+        <v>330.98</v>
+      </c>
+      <c r="E642" t="n">
+        <v>329.18</v>
+      </c>
+      <c r="F642" t="n">
+        <v>328.25</v>
+      </c>
+      <c r="G642" t="n">
+        <v>328.26</v>
+      </c>
+      <c r="H642" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="I642" t="n">
+        <v>336.91</v>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23534,7 +23570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B727"/>
+  <dimension ref="A1:B728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30807,6 +30843,16 @@
       </c>
       <c r="B727" t="n">
         <v>0.48</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -30975,28 +31021,28 @@
         <v>0.0471</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3834259035940215</v>
+        <v>-0.3826314993906971</v>
       </c>
       <c r="J2" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K2" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3766482727621386</v>
+        <v>0.3762621275519942</v>
       </c>
       <c r="M2" t="n">
-        <v>2.612954140711783</v>
+        <v>2.612446084852873</v>
       </c>
       <c r="N2" t="n">
-        <v>10.59607516036365</v>
+        <v>10.58789407996953</v>
       </c>
       <c r="O2" t="n">
-        <v>3.255161310958898</v>
+        <v>3.253904436207297</v>
       </c>
       <c r="P2" t="n">
-        <v>348.3887084571402</v>
+        <v>348.378936761722</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31057,28 +31103,28 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3922403487676768</v>
+        <v>-0.3923808871433755</v>
       </c>
       <c r="J3" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K3" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4004840681244188</v>
+        <v>0.4014405750280886</v>
       </c>
       <c r="M3" t="n">
-        <v>2.468927445414539</v>
+        <v>2.465753117596593</v>
       </c>
       <c r="N3" t="n">
-        <v>10.03009303658518</v>
+        <v>10.01470678099136</v>
       </c>
       <c r="O3" t="n">
-        <v>3.167032212748266</v>
+        <v>3.164602152086635</v>
       </c>
       <c r="P3" t="n">
-        <v>344.5544416869072</v>
+        <v>344.5561704015794</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31139,28 +31185,28 @@
         <v>0.1531</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.270691523821235</v>
+        <v>-0.2708720020926229</v>
       </c>
       <c r="J4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L4" t="n">
-        <v>0.113956173762371</v>
+        <v>0.1144222237524648</v>
       </c>
       <c r="M4" t="n">
-        <v>3.994778196601261</v>
+        <v>3.989378518861459</v>
       </c>
       <c r="N4" t="n">
-        <v>24.81141898340174</v>
+        <v>24.7731425696891</v>
       </c>
       <c r="O4" t="n">
-        <v>4.981106200775259</v>
+        <v>4.977262557841318</v>
       </c>
       <c r="P4" t="n">
-        <v>338.6637348137401</v>
+        <v>338.6659548154599</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31221,28 +31267,28 @@
         <v>0.1453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4709518046694099</v>
+        <v>-0.4720972238684749</v>
       </c>
       <c r="J5" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K5" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5092856291489938</v>
+        <v>0.5108559923758407</v>
       </c>
       <c r="M5" t="n">
-        <v>2.361832623630658</v>
+        <v>2.363441882697395</v>
       </c>
       <c r="N5" t="n">
-        <v>9.306903904328621</v>
+        <v>9.309742731492472</v>
       </c>
       <c r="O5" t="n">
-        <v>3.050721866104582</v>
+        <v>3.051187102013325</v>
       </c>
       <c r="P5" t="n">
-        <v>344.9705672259662</v>
+        <v>344.9846566372415</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31299,28 +31345,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4235367526924727</v>
+        <v>-0.4250583226135599</v>
       </c>
       <c r="J6" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K6" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4679272518197996</v>
+        <v>0.4696745196406035</v>
       </c>
       <c r="M6" t="n">
-        <v>2.37117725489131</v>
+        <v>2.373915083415398</v>
       </c>
       <c r="N6" t="n">
-        <v>8.883003340830712</v>
+        <v>8.899776151429339</v>
       </c>
       <c r="O6" t="n">
-        <v>2.980436770144724</v>
+        <v>2.983249260693672</v>
       </c>
       <c r="P6" t="n">
-        <v>343.8882980711678</v>
+        <v>343.9070143843042</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31377,28 +31423,28 @@
         <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5515825024222067</v>
+        <v>-0.553196981407742</v>
       </c>
       <c r="J7" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K7" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6639086746616307</v>
+        <v>0.6648008631722274</v>
       </c>
       <c r="M7" t="n">
-        <v>2.069212301421038</v>
+        <v>2.073562248402614</v>
       </c>
       <c r="N7" t="n">
-        <v>6.707410176461647</v>
+        <v>6.7314319749563</v>
       </c>
       <c r="O7" t="n">
-        <v>2.589866826008945</v>
+        <v>2.594500332425552</v>
       </c>
       <c r="P7" t="n">
-        <v>347.5557057865037</v>
+        <v>347.5755649423838</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31459,28 +31505,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5356823722645356</v>
+        <v>-0.5363572097920994</v>
       </c>
       <c r="J8" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K8" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5272753098874021</v>
+        <v>0.5285890418129755</v>
       </c>
       <c r="M8" t="n">
-        <v>2.65265735424289</v>
+        <v>2.650969283669329</v>
       </c>
       <c r="N8" t="n">
-        <v>11.20393303587971</v>
+        <v>11.19247943178751</v>
       </c>
       <c r="O8" t="n">
-        <v>3.347227664184154</v>
+        <v>3.345516317668696</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9302164782109</v>
+        <v>346.9385174246919</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -31541,28 +31587,28 @@
         <v>0.0601</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4050634792228224</v>
+        <v>-0.4052705033405017</v>
       </c>
       <c r="J9" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K9" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3665177833003808</v>
+        <v>0.3675092626516094</v>
       </c>
       <c r="M9" t="n">
-        <v>2.751270585707663</v>
+        <v>2.747838358874682</v>
       </c>
       <c r="N9" t="n">
-        <v>12.35010066609217</v>
+        <v>12.33140078282898</v>
       </c>
       <c r="O9" t="n">
-        <v>3.514271000661755</v>
+        <v>3.511609429140573</v>
       </c>
       <c r="P9" t="n">
-        <v>348.2189243799835</v>
+        <v>348.2214709131133</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -31604,7 +31650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J641"/>
+  <dimension ref="A1:J642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64939,6 +64985,58 @@
         </is>
       </c>
     </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-45.21644868239843,170.8880576559591</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-45.21676749306133,170.88728774769555</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-45.21702047935748,170.8864782654961</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-45.21726894145322,170.88565105617585</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-45.21776350418851,170.88503405020856</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>-45.218320989726934,170.88456524265516</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>-45.21891799089622,170.8842344400412</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>-45.2195215928727,170.88394920132288</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0478/nzd0478.xlsx
+++ b/data/nzd0478/nzd0478.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J642"/>
+  <dimension ref="A1:J646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23554,6 +23554,150 @@
         <v>336.91</v>
       </c>
       <c r="J642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>341.02</v>
+      </c>
+      <c r="C643" t="n">
+        <v>333.99</v>
+      </c>
+      <c r="D643" t="n">
+        <v>331.21</v>
+      </c>
+      <c r="E643" t="n">
+        <v>329.44</v>
+      </c>
+      <c r="F643" t="n">
+        <v>327.51</v>
+      </c>
+      <c r="G643" t="n">
+        <v>328.33</v>
+      </c>
+      <c r="H643" t="n">
+        <v>330.96</v>
+      </c>
+      <c r="I643" t="n">
+        <v>337.06</v>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="C644" t="n">
+        <v>334</v>
+      </c>
+      <c r="D644" t="n">
+        <v>332.21</v>
+      </c>
+      <c r="E644" t="n">
+        <v>329.93</v>
+      </c>
+      <c r="F644" t="n">
+        <v>327.65</v>
+      </c>
+      <c r="G644" t="n">
+        <v>328.61</v>
+      </c>
+      <c r="H644" t="n">
+        <v>330.97</v>
+      </c>
+      <c r="I644" t="n">
+        <v>336.62</v>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>340.7</v>
+      </c>
+      <c r="C645" t="n">
+        <v>333.77</v>
+      </c>
+      <c r="D645" t="n">
+        <v>331.04</v>
+      </c>
+      <c r="E645" t="n">
+        <v>328.26</v>
+      </c>
+      <c r="F645" t="n">
+        <v>326.04</v>
+      </c>
+      <c r="G645" t="n">
+        <v>327.18</v>
+      </c>
+      <c r="H645" t="n">
+        <v>330.44</v>
+      </c>
+      <c r="I645" t="n">
+        <v>335.84</v>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>340.97</v>
+      </c>
+      <c r="C646" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="D646" t="n">
+        <v>332.33</v>
+      </c>
+      <c r="E646" t="n">
+        <v>328.19</v>
+      </c>
+      <c r="F646" t="n">
+        <v>325.61</v>
+      </c>
+      <c r="G646" t="n">
+        <v>327.43</v>
+      </c>
+      <c r="H646" t="n">
+        <v>331.22</v>
+      </c>
+      <c r="I646" t="n">
+        <v>336.74</v>
+      </c>
+      <c r="J646" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23570,7 +23714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B728"/>
+  <dimension ref="A1:B732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30853,6 +30997,46 @@
       </c>
       <c r="B728" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -31021,28 +31205,28 @@
         <v>0.0471</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3826314993906971</v>
+        <v>-0.3788781422053498</v>
       </c>
       <c r="J2" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K2" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3762621275519942</v>
+        <v>0.3737035552876569</v>
       </c>
       <c r="M2" t="n">
-        <v>2.612446084852873</v>
+        <v>2.612870929562438</v>
       </c>
       <c r="N2" t="n">
-        <v>10.58789407996953</v>
+        <v>10.56896117599983</v>
       </c>
       <c r="O2" t="n">
-        <v>3.253904436207297</v>
+        <v>3.250993875109553</v>
       </c>
       <c r="P2" t="n">
-        <v>348.378936761722</v>
+        <v>348.332592630319</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31103,28 +31287,28 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3923808871433755</v>
+        <v>-0.3925306467551214</v>
       </c>
       <c r="J3" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K3" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4014405750280886</v>
+        <v>0.4047983354651657</v>
       </c>
       <c r="M3" t="n">
-        <v>2.465753117596593</v>
+        <v>2.45192397491238</v>
       </c>
       <c r="N3" t="n">
-        <v>10.01470678099136</v>
+        <v>9.95297795698119</v>
       </c>
       <c r="O3" t="n">
-        <v>3.164602152086635</v>
+        <v>3.154834061718808</v>
       </c>
       <c r="P3" t="n">
-        <v>344.5561704015794</v>
+        <v>344.5580179754143</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31185,28 +31369,28 @@
         <v>0.1531</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2708720020926229</v>
+        <v>-0.2705774052295646</v>
       </c>
       <c r="J4" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K4" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1144222237524648</v>
+        <v>0.1155372029064015</v>
       </c>
       <c r="M4" t="n">
-        <v>3.989378518861459</v>
+        <v>3.968190988063024</v>
       </c>
       <c r="N4" t="n">
-        <v>24.7731425696891</v>
+        <v>24.6218827884521</v>
       </c>
       <c r="O4" t="n">
-        <v>4.977262557841318</v>
+        <v>4.962044214681294</v>
       </c>
       <c r="P4" t="n">
-        <v>338.6659548154599</v>
+        <v>338.6623133278484</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31267,28 +31451,28 @@
         <v>0.1453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4720972238684749</v>
+        <v>-0.4768530527414775</v>
       </c>
       <c r="J5" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K5" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5108559923758407</v>
+        <v>0.5170728704658072</v>
       </c>
       <c r="M5" t="n">
-        <v>2.363441882697395</v>
+        <v>2.370383889675556</v>
       </c>
       <c r="N5" t="n">
-        <v>9.309742731492472</v>
+        <v>9.329953291059629</v>
       </c>
       <c r="O5" t="n">
-        <v>3.051187102013325</v>
+        <v>3.054497223940403</v>
       </c>
       <c r="P5" t="n">
-        <v>344.9846566372415</v>
+        <v>345.0433893102941</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31345,28 +31529,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4250583226135599</v>
+        <v>-0.4331085323296795</v>
       </c>
       <c r="J6" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K6" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4696745196406035</v>
+        <v>0.4762433361516873</v>
       </c>
       <c r="M6" t="n">
-        <v>2.373915083415398</v>
+        <v>2.393097152511072</v>
       </c>
       <c r="N6" t="n">
-        <v>8.899776151429339</v>
+        <v>9.063054930229171</v>
       </c>
       <c r="O6" t="n">
-        <v>2.983249260693672</v>
+        <v>3.010490812181491</v>
       </c>
       <c r="P6" t="n">
-        <v>343.9070143843042</v>
+        <v>344.0064283950339</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31423,28 +31607,28 @@
         <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.553196981407742</v>
+        <v>-0.5600005279009895</v>
       </c>
       <c r="J7" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K7" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6648008631722274</v>
+        <v>0.6680916706710414</v>
       </c>
       <c r="M7" t="n">
-        <v>2.073562248402614</v>
+        <v>2.092300042635805</v>
       </c>
       <c r="N7" t="n">
-        <v>6.7314319749563</v>
+        <v>6.844464105220944</v>
       </c>
       <c r="O7" t="n">
-        <v>2.594500332425552</v>
+        <v>2.616192673566101</v>
       </c>
       <c r="P7" t="n">
-        <v>347.5755649423838</v>
+        <v>347.6595800609916</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31505,28 +31689,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5363572097920994</v>
+        <v>-0.5388103036443851</v>
       </c>
       <c r="J8" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K8" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5285890418129755</v>
+        <v>0.5337008748855929</v>
       </c>
       <c r="M8" t="n">
-        <v>2.650969283669329</v>
+        <v>2.643389808693598</v>
       </c>
       <c r="N8" t="n">
-        <v>11.19247943178751</v>
+        <v>11.14343164910307</v>
       </c>
       <c r="O8" t="n">
-        <v>3.345516317668696</v>
+        <v>3.338177893567548</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9385174246919</v>
+        <v>346.9688069729454</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -31587,28 +31771,28 @@
         <v>0.0601</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4052705033405017</v>
+        <v>-0.4064984748064975</v>
       </c>
       <c r="J9" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K9" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3675092626516094</v>
+        <v>0.3718842088700096</v>
       </c>
       <c r="M9" t="n">
-        <v>2.747838358874682</v>
+        <v>2.735808938065251</v>
       </c>
       <c r="N9" t="n">
-        <v>12.33140078282898</v>
+        <v>12.26112439886073</v>
       </c>
       <c r="O9" t="n">
-        <v>3.511609429140573</v>
+        <v>3.501588839207243</v>
       </c>
       <c r="P9" t="n">
-        <v>348.2214709131133</v>
+        <v>348.2366366980294</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -31650,7 +31834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J642"/>
+  <dimension ref="A1:J646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65037,6 +65221,214 @@
         </is>
       </c>
     </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-45.2164519983631,170.8880609442595</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-45.21676912681746,170.8872890912794</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-45.21702236565492,170.88647947053565</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-45.21727083282329,170.88565300466726</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>-45.21775953988677,170.88502648017266</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>-45.218321285468534,170.8845660295582</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>-45.21891858464236,170.88423629589548</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>-45.21952214951252,170.8839509412026</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-45.21645391425378,170.88806284416657</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-45.21676920461537,170.8872891552596</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-45.21703056694799,170.88648470983892</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-45.21727439732831,170.88565667682457</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>-45.217760289889846,170.88502791234154</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>-45.21832246843489,170.8845691771703</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>-45.21891862175151,170.88423641188638</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>-45.21952051670227,170.88394583755544</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-45.21644964034379,170.88805860591253</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-45.21676741526343,170.88728768371539</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-45.21702097143508,170.8864785798542</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-45.21726224891278,170.88564416151485</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-45.2177516648535,170.88501144240175</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>-45.218316426855836,170.88455310186694</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>-45.21891665496729,170.8842302643693</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>-45.21951762217443,170.88393679018165</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-45.2164516299226,170.88806057889278</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-45.21677208313801,170.88729152252654</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-45.21703155110314,170.88648533855545</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-45.21726173969774,170.88564363692112</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-45.21774936127197,170.88500704359882</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>-45.21831748307611,170.88455591223442</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>-45.2189195494798,170.88423931165875</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>-45.21952096201419,170.8839472294592</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0478/nzd0478.xlsx
+++ b/data/nzd0478/nzd0478.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J646"/>
+  <dimension ref="A1:J648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23698,6 +23698,78 @@
         <v>336.74</v>
       </c>
       <c r="J646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>339.91</v>
+      </c>
+      <c r="C647" t="n">
+        <v>333.47</v>
+      </c>
+      <c r="D647" t="n">
+        <v>331.25</v>
+      </c>
+      <c r="E647" t="n">
+        <v>326.53</v>
+      </c>
+      <c r="F647" t="n">
+        <v>324.43</v>
+      </c>
+      <c r="G647" t="n">
+        <v>327.66</v>
+      </c>
+      <c r="H647" t="n">
+        <v>331.77</v>
+      </c>
+      <c r="I647" t="n">
+        <v>337.7</v>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:09+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>340.11</v>
+      </c>
+      <c r="C648" t="n">
+        <v>334.54</v>
+      </c>
+      <c r="D648" t="n">
+        <v>331.99</v>
+      </c>
+      <c r="E648" t="n">
+        <v>325.64</v>
+      </c>
+      <c r="F648" t="n">
+        <v>325.17</v>
+      </c>
+      <c r="G648" t="n">
+        <v>328.31</v>
+      </c>
+      <c r="H648" t="n">
+        <v>332.18</v>
+      </c>
+      <c r="I648" t="n">
+        <v>337.63</v>
+      </c>
+      <c r="J648" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23714,7 +23786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B732"/>
+  <dimension ref="A1:B734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31037,6 +31109,26 @@
       </c>
       <c r="B732" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -31205,28 +31297,28 @@
         <v>0.0471</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3788781422053498</v>
+        <v>-0.3776733679831946</v>
       </c>
       <c r="J2" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K2" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3737035552876569</v>
+        <v>0.3735520866751838</v>
       </c>
       <c r="M2" t="n">
-        <v>2.612870929562438</v>
+        <v>2.61007940939916</v>
       </c>
       <c r="N2" t="n">
-        <v>10.56896117599983</v>
+        <v>10.54593311952903</v>
       </c>
       <c r="O2" t="n">
-        <v>3.250993875109553</v>
+        <v>3.247450248969032</v>
       </c>
       <c r="P2" t="n">
-        <v>348.332592630319</v>
+        <v>348.3176542013401</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31287,28 +31379,28 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3925306467551214</v>
+        <v>-0.392593612454462</v>
       </c>
       <c r="J3" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K3" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4047983354651657</v>
+        <v>0.4064533307662854</v>
       </c>
       <c r="M3" t="n">
-        <v>2.45192397491238</v>
+        <v>2.44602860239991</v>
       </c>
       <c r="N3" t="n">
-        <v>9.95297795698119</v>
+        <v>9.923140355523325</v>
       </c>
       <c r="O3" t="n">
-        <v>3.154834061718808</v>
+        <v>3.150101642094001</v>
       </c>
       <c r="P3" t="n">
-        <v>344.5580179754143</v>
+        <v>344.5587970427217</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31369,28 +31461,28 @@
         <v>0.1531</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2705774052295646</v>
+        <v>-0.2704626943986946</v>
       </c>
       <c r="J4" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K4" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1155372029064015</v>
+        <v>0.1161279768584401</v>
       </c>
       <c r="M4" t="n">
-        <v>3.968190988063024</v>
+        <v>3.957064841657256</v>
       </c>
       <c r="N4" t="n">
-        <v>24.6218827884521</v>
+        <v>24.54628420067226</v>
       </c>
       <c r="O4" t="n">
-        <v>4.962044214681294</v>
+        <v>4.954420672558222</v>
       </c>
       <c r="P4" t="n">
-        <v>338.6623133278484</v>
+        <v>338.6608898844008</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31451,28 +31543,28 @@
         <v>0.1453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4768530527414775</v>
+        <v>-0.4811057486107665</v>
       </c>
       <c r="J5" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K5" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5170728704658072</v>
+        <v>0.5199546947794806</v>
       </c>
       <c r="M5" t="n">
-        <v>2.370383889675556</v>
+        <v>2.382304609691317</v>
       </c>
       <c r="N5" t="n">
-        <v>9.329953291059629</v>
+        <v>9.421418712365828</v>
       </c>
       <c r="O5" t="n">
-        <v>3.054497223940403</v>
+        <v>3.069432962676629</v>
       </c>
       <c r="P5" t="n">
-        <v>345.0433893102941</v>
+        <v>345.0961202136268</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31529,28 +31621,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4331085323296795</v>
+        <v>-0.4383207563556922</v>
       </c>
       <c r="J6" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K6" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4762433361516873</v>
+        <v>0.4789384305599546</v>
       </c>
       <c r="M6" t="n">
-        <v>2.393097152511072</v>
+        <v>2.40796363982757</v>
       </c>
       <c r="N6" t="n">
-        <v>9.063054930229171</v>
+        <v>9.215351823603026</v>
       </c>
       <c r="O6" t="n">
-        <v>3.010490812181491</v>
+        <v>3.03567979596054</v>
       </c>
       <c r="P6" t="n">
-        <v>344.0064283950339</v>
+        <v>344.0710540912198</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31607,28 +31699,28 @@
         <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5600005279009895</v>
+        <v>-0.5632337505090874</v>
       </c>
       <c r="J7" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K7" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6680916706710414</v>
+        <v>0.6698653099531007</v>
       </c>
       <c r="M7" t="n">
-        <v>2.092300042635805</v>
+        <v>2.100915817615314</v>
       </c>
       <c r="N7" t="n">
-        <v>6.844464105220944</v>
+        <v>6.892860770291529</v>
       </c>
       <c r="O7" t="n">
-        <v>2.616192673566101</v>
+        <v>2.625425826469209</v>
       </c>
       <c r="P7" t="n">
-        <v>347.6595800609916</v>
+        <v>347.6996680771158</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31689,28 +31781,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5388103036443851</v>
+        <v>-0.5392448346828034</v>
       </c>
       <c r="J8" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K8" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5337008748855929</v>
+        <v>0.5357222402943561</v>
       </c>
       <c r="M8" t="n">
-        <v>2.643389808693598</v>
+        <v>2.636768683563927</v>
       </c>
       <c r="N8" t="n">
-        <v>11.14343164910307</v>
+        <v>11.1103740783989</v>
       </c>
       <c r="O8" t="n">
-        <v>3.338177893567548</v>
+        <v>3.333222776593083</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9688069729454</v>
+        <v>346.9741941179194</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -31771,28 +31863,28 @@
         <v>0.0601</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4064984748064975</v>
+        <v>-0.4063223350871323</v>
       </c>
       <c r="J9" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K9" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3718842088700096</v>
+        <v>0.3732291542518819</v>
       </c>
       <c r="M9" t="n">
-        <v>2.735808938065251</v>
+        <v>2.728229511939935</v>
       </c>
       <c r="N9" t="n">
-        <v>12.26112439886073</v>
+        <v>12.22343050919765</v>
       </c>
       <c r="O9" t="n">
-        <v>3.501588839207243</v>
+        <v>3.496202298093983</v>
       </c>
       <c r="P9" t="n">
-        <v>348.2366366980294</v>
+        <v>348.2344528057359</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -31834,7 +31926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J646"/>
+  <dimension ref="A1:J648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65429,6 +65521,110 @@
         </is>
       </c>
     </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-45.21644381898341,170.88805283311925</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-45.2167650813261,170.88728576431</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-45.21702269370666,170.88647968010775</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-45.21724966402588,170.88563119655882</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-45.21774303981485,170.884994972467</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>-45.218318454798705,170.8845584977726</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>-45.218921590481784,170.88424569115824</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>-45.21952452450888,170.88395836468993</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:09+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-45.216445292745554,170.88805429458577</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-45.216773405702455,170.8872926101898</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-45.217028762663546,170.8864835571921</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-45.21724318971937,170.88562452672818</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-45.21774700411861,170.8850025424985</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>-45.218321200970934,170.88456580472877</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>-45.218923111955775,170.88425044678547</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>-45.21952426474368,170.88395755274598</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0478/nzd0478.xlsx
+++ b/data/nzd0478/nzd0478.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J648"/>
+  <dimension ref="A1:J654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23770,6 +23770,222 @@
         <v>337.63</v>
       </c>
       <c r="J648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>339.56</v>
+      </c>
+      <c r="C649" t="n">
+        <v>334.08</v>
+      </c>
+      <c r="D649" t="n">
+        <v>331.34</v>
+      </c>
+      <c r="E649" t="n">
+        <v>325.23</v>
+      </c>
+      <c r="F649" t="n">
+        <v>324.86</v>
+      </c>
+      <c r="G649" t="n">
+        <v>328.27</v>
+      </c>
+      <c r="H649" t="n">
+        <v>332.13</v>
+      </c>
+      <c r="I649" t="n">
+        <v>337.54</v>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>339.67</v>
+      </c>
+      <c r="C650" t="n">
+        <v>333.77</v>
+      </c>
+      <c r="D650" t="n">
+        <v>331.07</v>
+      </c>
+      <c r="E650" t="n">
+        <v>324.9</v>
+      </c>
+      <c r="F650" t="n">
+        <v>324.89</v>
+      </c>
+      <c r="G650" t="n">
+        <v>329.04</v>
+      </c>
+      <c r="H650" t="n">
+        <v>331.98</v>
+      </c>
+      <c r="I650" t="n">
+        <v>337.74</v>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:53+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>340.33</v>
+      </c>
+      <c r="C651" t="n">
+        <v>334.66</v>
+      </c>
+      <c r="D651" t="n">
+        <v>331.83</v>
+      </c>
+      <c r="E651" t="n">
+        <v>325.43</v>
+      </c>
+      <c r="F651" t="n">
+        <v>326.02</v>
+      </c>
+      <c r="G651" t="n">
+        <v>329.81</v>
+      </c>
+      <c r="H651" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="I651" t="n">
+        <v>338.03</v>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>339.66</v>
+      </c>
+      <c r="C652" t="n">
+        <v>333.93</v>
+      </c>
+      <c r="D652" t="n">
+        <v>330.93</v>
+      </c>
+      <c r="E652" t="n">
+        <v>325.42</v>
+      </c>
+      <c r="F652" t="n">
+        <v>326.25</v>
+      </c>
+      <c r="G652" t="n">
+        <v>329.55</v>
+      </c>
+      <c r="H652" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="I652" t="n">
+        <v>337.34</v>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>340.37</v>
+      </c>
+      <c r="C653" t="n">
+        <v>334.94</v>
+      </c>
+      <c r="D653" t="n">
+        <v>331.31</v>
+      </c>
+      <c r="E653" t="n">
+        <v>326.04</v>
+      </c>
+      <c r="F653" t="n">
+        <v>327.46</v>
+      </c>
+      <c r="G653" t="n">
+        <v>330.42</v>
+      </c>
+      <c r="H653" t="n">
+        <v>333.8</v>
+      </c>
+      <c r="I653" t="n">
+        <v>338.17</v>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>343.03</v>
+      </c>
+      <c r="C654" t="n">
+        <v>337.02</v>
+      </c>
+      <c r="D654" t="n">
+        <v>331.31</v>
+      </c>
+      <c r="E654" t="n">
+        <v>326.49</v>
+      </c>
+      <c r="F654" t="n">
+        <v>328.62</v>
+      </c>
+      <c r="G654" t="n">
+        <v>331.14</v>
+      </c>
+      <c r="H654" t="n">
+        <v>334.41</v>
+      </c>
+      <c r="I654" t="n">
+        <v>339.25</v>
+      </c>
+      <c r="J654" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23786,7 +24002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B734"/>
+  <dimension ref="A1:B740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31129,6 +31345,66 @@
       </c>
       <c r="B734" t="n">
         <v>-0.12</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -31297,28 +31573,28 @@
         <v>0.0471</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3776733679831946</v>
+        <v>-0.3732892190014694</v>
       </c>
       <c r="J2" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K2" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3735520866751838</v>
+        <v>0.3714131211952185</v>
       </c>
       <c r="M2" t="n">
-        <v>2.61007940939916</v>
+        <v>2.605086423600505</v>
       </c>
       <c r="N2" t="n">
-        <v>10.54593311952903</v>
+        <v>10.50563748095168</v>
       </c>
       <c r="O2" t="n">
-        <v>3.247450248969032</v>
+        <v>3.241240114670877</v>
       </c>
       <c r="P2" t="n">
-        <v>348.3176542013401</v>
+        <v>348.2631783103491</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31379,28 +31655,28 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.392593612454462</v>
+        <v>-0.3912865676050972</v>
       </c>
       <c r="J3" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K3" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4064533307662854</v>
+        <v>0.4092059099170704</v>
       </c>
       <c r="M3" t="n">
-        <v>2.44602860239991</v>
+        <v>2.430732834519033</v>
       </c>
       <c r="N3" t="n">
-        <v>9.923140355523325</v>
+        <v>9.847082369620942</v>
       </c>
       <c r="O3" t="n">
-        <v>3.150101642094001</v>
+        <v>3.138006113700377</v>
       </c>
       <c r="P3" t="n">
-        <v>344.5587970427217</v>
+        <v>344.5425443111918</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31461,28 +31737,28 @@
         <v>0.1531</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2704626943986946</v>
+        <v>-0.2707497352085311</v>
       </c>
       <c r="J4" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K4" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1161279768584401</v>
+        <v>0.1183726975260136</v>
       </c>
       <c r="M4" t="n">
-        <v>3.957064841657256</v>
+        <v>3.923191903572552</v>
       </c>
       <c r="N4" t="n">
-        <v>24.54628420067226</v>
+        <v>24.32164889256128</v>
       </c>
       <c r="O4" t="n">
-        <v>4.954420672558222</v>
+        <v>4.93169837810072</v>
       </c>
       <c r="P4" t="n">
-        <v>338.6608898844008</v>
+        <v>338.6644563054398</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31543,28 +31819,28 @@
         <v>0.1453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4811057486107665</v>
+        <v>-0.4943909162461134</v>
       </c>
       <c r="J5" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K5" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5199546947794806</v>
+        <v>0.5279691005137683</v>
       </c>
       <c r="M5" t="n">
-        <v>2.382304609691317</v>
+        <v>2.420396091550303</v>
       </c>
       <c r="N5" t="n">
-        <v>9.421418712365828</v>
+        <v>9.734784344254658</v>
       </c>
       <c r="O5" t="n">
-        <v>3.069432962676629</v>
+        <v>3.120061593022589</v>
       </c>
       <c r="P5" t="n">
-        <v>345.0961202136268</v>
+        <v>345.2611306465656</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31621,28 +31897,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4383207563556922</v>
+        <v>-0.4503074685121649</v>
       </c>
       <c r="J6" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K6" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4789384305599546</v>
+        <v>0.4881668155821841</v>
       </c>
       <c r="M6" t="n">
-        <v>2.40796363982757</v>
+        <v>2.438328333423111</v>
       </c>
       <c r="N6" t="n">
-        <v>9.215351823603026</v>
+        <v>9.471132948747544</v>
       </c>
       <c r="O6" t="n">
-        <v>3.03567979596054</v>
+        <v>3.077520584618004</v>
       </c>
       <c r="P6" t="n">
-        <v>344.0710540912198</v>
+        <v>344.2199176442643</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31699,28 +31975,28 @@
         <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5632337505090874</v>
+        <v>-0.5691279351302652</v>
       </c>
       <c r="J7" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K7" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6698653099531007</v>
+        <v>0.6759982637733972</v>
       </c>
       <c r="M7" t="n">
-        <v>2.100915817615314</v>
+        <v>2.109658661513536</v>
       </c>
       <c r="N7" t="n">
-        <v>6.892860770291529</v>
+        <v>6.915841163537743</v>
       </c>
       <c r="O7" t="n">
-        <v>2.625425826469209</v>
+        <v>2.629798692588036</v>
       </c>
       <c r="P7" t="n">
-        <v>347.6996680771158</v>
+        <v>347.7728626868718</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31781,28 +32057,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5392448346828034</v>
+        <v>-0.5384944534829916</v>
       </c>
       <c r="J8" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K8" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5357222402943561</v>
+        <v>0.539711257288489</v>
       </c>
       <c r="M8" t="n">
-        <v>2.636768683563927</v>
+        <v>2.61998983944528</v>
       </c>
       <c r="N8" t="n">
-        <v>11.1103740783989</v>
+        <v>11.01678293974782</v>
       </c>
       <c r="O8" t="n">
-        <v>3.333222776593083</v>
+        <v>3.319153949389485</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9741941179194</v>
+        <v>346.9648554224714</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -31863,28 +32139,28 @@
         <v>0.0601</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4063223350871323</v>
+        <v>-0.4050786339244081</v>
       </c>
       <c r="J9" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K9" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3732291542518819</v>
+        <v>0.3762491094520085</v>
       </c>
       <c r="M9" t="n">
-        <v>2.728229511939935</v>
+        <v>2.70944982269144</v>
       </c>
       <c r="N9" t="n">
-        <v>12.22343050919765</v>
+        <v>12.11819170448168</v>
       </c>
       <c r="O9" t="n">
-        <v>3.496202298093983</v>
+        <v>3.481119317759976</v>
       </c>
       <c r="P9" t="n">
-        <v>348.2344528057359</v>
+        <v>348.2189949520083</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -31926,7 +32202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J648"/>
+  <dimension ref="A1:J654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65625,6 +65901,318 @@
         </is>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-45.21644123989961,170.88805027555296</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-45.21676982699864,170.88728966710107</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-45.21702343182304,170.88648015164497</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-45.217240207173546,170.88562145411007</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>-45.217745343396814,170.88499937126898</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>-45.21832103197574,170.8845653550699</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>-45.21892292641017,170.88424986683094</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>-45.21952393075984,170.88395650881804</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-45.21644205046882,170.88805107935949</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-45.21676741526343,170.88728768371539</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-45.21702121747388,170.8864787370333</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>-45.21723780658783,170.88561898102745</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>-45.21774550411184,170.88499967816216</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>-45.21832428513304,170.88457401100348</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>-45.21892236977336,170.8842481269673</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>-45.219524672946136,170.8839588286579</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:53+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-45.2164469138839,170.88805590219906</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-45.21677433927736,170.88729337795215</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-45.21702745045665,170.88648271890352</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-45.21724166207395,170.88562295294813</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>-45.217751557710166,170.88501123780625</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>-45.218327538289735,170.88458266693806</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>-45.21892552404828,170.88425798619502</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>-45.21952574911619,170.88396219242586</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-45.21644197678071,170.88805100628616</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-45.21676866003,170.88728870739828</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-45.21702006929282,170.886478003531</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-45.217241589328935,170.88562287800622</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>-45.21775278985836,170.8850135906545</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>-45.21832643982132,170.88457974415482</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>-45.21892459632044,170.88425508642203</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>-45.2195231885735,170.88395418897824</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>-45.21644720863632,170.8880561944924</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>-45.21677651761876,170.8872951693977</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>-45.21702318578425,170.88647999446593</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-45.2172460995201,170.88562752440467</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>-45.21775927202852,170.88502596868378</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>-45.21833011546536,170.88458952423758</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>-45.21892912363158,170.8842692373151</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>-45.21952626864652,170.88396381631384</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>-45.216466809670926,170.88807563200587</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>-45.21679269958262,170.88730847728323</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>-45.21702318578425,170.88647999446593</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-45.21724937304584,170.8856308967911</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>-45.2177654863392,170.8850378352269</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>-45.21833315737703,170.88459761810014</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>-45.218931387286496,170.8842763127625</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>-45.219530276451195,170.8839763434509</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0478/nzd0478.xlsx
+++ b/data/nzd0478/nzd0478.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J654"/>
+  <dimension ref="A1:J657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23986,6 +23986,114 @@
         <v>339.25</v>
       </c>
       <c r="J654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>342.42</v>
+      </c>
+      <c r="C655" t="n">
+        <v>336.45</v>
+      </c>
+      <c r="D655" t="n">
+        <v>330.19</v>
+      </c>
+      <c r="E655" t="n">
+        <v>326.15</v>
+      </c>
+      <c r="F655" t="n">
+        <v>328.58</v>
+      </c>
+      <c r="G655" t="n">
+        <v>330.96</v>
+      </c>
+      <c r="H655" t="n">
+        <v>333.94</v>
+      </c>
+      <c r="I655" t="n">
+        <v>339.42</v>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:35+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>344.25</v>
+      </c>
+      <c r="C656" t="n">
+        <v>338.37</v>
+      </c>
+      <c r="D656" t="n">
+        <v>329.55</v>
+      </c>
+      <c r="E656" t="n">
+        <v>326.14</v>
+      </c>
+      <c r="F656" t="n">
+        <v>329.67</v>
+      </c>
+      <c r="G656" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="H656" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="I656" t="n">
+        <v>337.68</v>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>344.25</v>
+      </c>
+      <c r="C657" t="n">
+        <v>337.78</v>
+      </c>
+      <c r="D657" t="n">
+        <v>328.11</v>
+      </c>
+      <c r="E657" t="n">
+        <v>326.12</v>
+      </c>
+      <c r="F657" t="n">
+        <v>330.1</v>
+      </c>
+      <c r="G657" t="n">
+        <v>330.63</v>
+      </c>
+      <c r="H657" t="n">
+        <v>333.07</v>
+      </c>
+      <c r="I657" t="n">
+        <v>337.56</v>
+      </c>
+      <c r="J657" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24002,7 +24110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B740"/>
+  <dimension ref="A1:B744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31405,6 +31513,46 @@
       </c>
       <c r="B740" t="n">
         <v>-0.84</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -31573,28 +31721,28 @@
         <v>0.0471</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3732892190014694</v>
+        <v>-0.3679427602496794</v>
       </c>
       <c r="J2" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="K2" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3714131211952185</v>
+        <v>0.3640080549383468</v>
       </c>
       <c r="M2" t="n">
-        <v>2.605086423600505</v>
+        <v>2.616070354184429</v>
       </c>
       <c r="N2" t="n">
-        <v>10.50563748095168</v>
+        <v>10.5917007775302</v>
       </c>
       <c r="O2" t="n">
-        <v>3.241240114670877</v>
+        <v>3.254489326688629</v>
       </c>
       <c r="P2" t="n">
-        <v>348.2631783103491</v>
+        <v>348.1964870927615</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31655,28 +31803,28 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3912865676050972</v>
+        <v>-0.3878322120452604</v>
       </c>
       <c r="J3" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="K3" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4092059099170704</v>
+        <v>0.4058642931758903</v>
       </c>
       <c r="M3" t="n">
-        <v>2.430732834519033</v>
+        <v>2.434562214574425</v>
       </c>
       <c r="N3" t="n">
-        <v>9.847082369620942</v>
+        <v>9.859550622555334</v>
       </c>
       <c r="O3" t="n">
-        <v>3.138006113700377</v>
+        <v>3.139992137339731</v>
       </c>
       <c r="P3" t="n">
-        <v>344.5425443111918</v>
+        <v>344.4994541886773</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31737,28 +31885,28 @@
         <v>0.1531</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2707497352085311</v>
+        <v>-0.2728588322426262</v>
       </c>
       <c r="J4" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="K4" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1183726975260136</v>
+        <v>0.1209303877896815</v>
       </c>
       <c r="M4" t="n">
-        <v>3.923191903572552</v>
+        <v>3.914763473524001</v>
       </c>
       <c r="N4" t="n">
-        <v>24.32164889256128</v>
+        <v>24.23418462354105</v>
       </c>
       <c r="O4" t="n">
-        <v>4.93169837810072</v>
+        <v>4.922822830809682</v>
       </c>
       <c r="P4" t="n">
-        <v>338.6644563054398</v>
+        <v>338.6907666447642</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31819,28 +31967,28 @@
         <v>0.1453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4943909162461134</v>
+        <v>-0.5002232482382021</v>
       </c>
       <c r="J5" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="K5" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5279691005137683</v>
+        <v>0.5322719800638683</v>
       </c>
       <c r="M5" t="n">
-        <v>2.420396091550303</v>
+        <v>2.435596257935175</v>
       </c>
       <c r="N5" t="n">
-        <v>9.734784344254658</v>
+        <v>9.845824380586572</v>
       </c>
       <c r="O5" t="n">
-        <v>3.120061593022589</v>
+        <v>3.137805663291876</v>
       </c>
       <c r="P5" t="n">
-        <v>345.2611306465656</v>
+        <v>345.3338783096543</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31897,28 +32045,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4503074685121649</v>
+        <v>-0.4529896304885886</v>
       </c>
       <c r="J6" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="K6" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4881668155821841</v>
+        <v>0.4926496128515311</v>
       </c>
       <c r="M6" t="n">
-        <v>2.438328333423111</v>
+        <v>2.439080786425003</v>
       </c>
       <c r="N6" t="n">
-        <v>9.471132948747544</v>
+        <v>9.462609742312495</v>
       </c>
       <c r="O6" t="n">
-        <v>3.077520584618004</v>
+        <v>3.076135520797563</v>
       </c>
       <c r="P6" t="n">
-        <v>344.2199176442643</v>
+        <v>344.2533698023522</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31975,28 +32123,28 @@
         <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5691279351302652</v>
+        <v>-0.5709064311365684</v>
       </c>
       <c r="J7" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="K7" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6759982637733972</v>
+        <v>0.6790285714897217</v>
       </c>
       <c r="M7" t="n">
-        <v>2.109658661513536</v>
+        <v>2.108512811071581</v>
       </c>
       <c r="N7" t="n">
-        <v>6.915841163537743</v>
+        <v>6.898787296817123</v>
       </c>
       <c r="O7" t="n">
-        <v>2.629798692588036</v>
+        <v>2.626554263063515</v>
       </c>
       <c r="P7" t="n">
-        <v>347.7728626868718</v>
+        <v>347.7950468648548</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32057,28 +32205,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5384944534829916</v>
+        <v>-0.5375995686375435</v>
       </c>
       <c r="J8" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="K8" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="L8" t="n">
-        <v>0.539711257288489</v>
+        <v>0.5412086698774421</v>
       </c>
       <c r="M8" t="n">
-        <v>2.61998983944528</v>
+        <v>2.612930375479773</v>
       </c>
       <c r="N8" t="n">
-        <v>11.01678293974782</v>
+        <v>10.97066208318667</v>
       </c>
       <c r="O8" t="n">
-        <v>3.319153949389485</v>
+        <v>3.312198980011115</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9648554224714</v>
+        <v>346.9536950115536</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32139,28 +32287,28 @@
         <v>0.0601</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4050786339244081</v>
+        <v>-0.4042303204044668</v>
       </c>
       <c r="J9" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="K9" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3762491094520085</v>
+        <v>0.3774249533699788</v>
       </c>
       <c r="M9" t="n">
-        <v>2.70944982269144</v>
+        <v>2.701208363445037</v>
       </c>
       <c r="N9" t="n">
-        <v>12.11819170448168</v>
+        <v>12.06933742859609</v>
       </c>
       <c r="O9" t="n">
-        <v>3.481119317759976</v>
+        <v>3.474095195672693</v>
       </c>
       <c r="P9" t="n">
-        <v>348.2189949520083</v>
+        <v>348.2084176631932</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32202,7 +32350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J654"/>
+  <dimension ref="A1:J657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,6 +66361,162 @@
         </is>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>-45.21646231469709,170.88807117452978</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-45.216788265102274,170.88730483041002</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>-45.21701400033576,170.88647412644778</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>-45.217246899715285,170.88562834876578</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>-45.21776527205265,170.88503742603572</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>-45.21833239689916,170.8845955946344</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>-45.21892964315897,170.8842708611882</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>-45.21953090730923,170.88397831531523</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:35+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>-45.216475799618046,170.88808454696007</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>-45.216803202298784,170.88731711461674</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>-45.217008751507926,170.88647077329543</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>-45.21724682697028,170.88562827382387</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>-45.21777111136076,170.88504857649667</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>-45.218330875943316,170.88459154770314</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>-45.2189272681764,170.88426343776848</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>-45.21952445029025,170.88395813270594</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>-45.216475799618046,170.88808454696007</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>-45.2167986122229,170.8873133397817</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>-45.21699694164497,170.88646322870477</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>-45.21724668148024,170.88562812394002</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>-45.21777341494073,170.88505297530298</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>-45.21833100268965,170.8845918849474</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>-45.21892641466693,170.88426076997717</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>-45.21952400497846,170.88395674080203</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
